--- a/tests/e2e/_fixtures/summary-7-11-ice.xlsx
+++ b/tests/e2e/_fixtures/summary-7-11-ice.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="สรุปยอดขาย" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,121 +413,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>วันที่</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ยอด</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ราคา</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ยอดเงินก่อน vat</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ยอดเงิน vat</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ยอดเงินรวม</t>
-        </is>
-      </c>
+          <t>สรุปยอดขาย 7-11  เดือน มิถุนายน 2569</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="D2" t="n">
-        <v>607</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42.49</v>
-      </c>
-      <c r="F2" t="n">
-        <v>649.49</v>
+          <t>วันที่</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ยอด</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ราคา</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ยอดเงินก่อน vat</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ยอดเงิน vat</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ยอดเงินรวม</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>19220</v>
       </c>
       <c r="C3" t="n">
         <v>6.07</v>
       </c>
       <c r="D3" t="n">
-        <v>1214</v>
+        <v>116665.4</v>
       </c>
       <c r="E3" t="n">
-        <v>84.98</v>
+        <v>8166.58</v>
       </c>
       <c r="F3" t="n">
-        <v>1298.98</v>
+        <v>124831.98</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>20200</v>
       </c>
       <c r="C4" t="n">
         <v>6.07</v>
       </c>
       <c r="D4" t="n">
-        <v>910.5</v>
+        <v>122614</v>
       </c>
       <c r="E4" t="n">
-        <v>63.74</v>
+        <v>8582.98</v>
       </c>
       <c r="F4" t="n">
-        <v>974.24</v>
+        <v>131196.98</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>รวม</t>
-        </is>
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6.07</v>
       </c>
       <c r="D5" t="n">
-        <v>2731.5</v>
+        <v>128684</v>
       </c>
       <c r="E5" t="n">
-        <v>191.21</v>
+        <v>9007.879999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2922.71</v>
+        <v>137691.88</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ยอดรวมทั้งหมด</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>367963.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25757.44</v>
+      </c>
+      <c r="F7" t="n">
+        <v>393720.84</v>
       </c>
     </row>
   </sheetData>
